--- a/Design-Files/OFP_USM_v1.5/BOM/Client-BOM-OFP_USM_v1.5.xlsx
+++ b/Design-Files/OFP_USM_v1.5/BOM/Client-BOM-OFP_USM_v1.5.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="85">
   <si>
     <t>#</t>
   </si>
@@ -259,6 +259,21 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>Peripheral</t>
+  </si>
+  <si>
+    <t>0.3mm 10P 0.5mm 60mm P=0.5mm FFC Cable (Flexible Flat Cable) ROHS</t>
+  </si>
+  <si>
+    <t>P=0.5mm</t>
+  </si>
+  <si>
+    <t>AB03A0100000180A</t>
+  </si>
+  <si>
+    <t>BZCN</t>
   </si>
 </sst>
 </file>
@@ -751,7 +766,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="4" customWidth="1"/>
@@ -762,7 +777,7 @@
     <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -847,7 +862,7 @@
     <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="11">
-        <f t="shared" ref="B4:B14" si="0">ROW(B4) - ROW($B$2)</f>
+        <f t="shared" ref="B4:B16" si="0">ROW(B4) - ROW($B$2)</f>
         <v>2</v>
       </c>
       <c r="C4" s="13" t="s">
@@ -1227,6 +1242,37 @@
         <v>1</v>
       </c>
       <c r="K15" s="7"/>
+    </row>
+    <row r="16" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="11">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="J16" s="9">
+        <v>1</v>
+      </c>
+      <c r="K16" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Design-Files/OFP_USM_v1.5/BOM/Client-BOM-OFP_USM_v1.5.xlsx
+++ b/Design-Files/OFP_USM_v1.5/BOM/Client-BOM-OFP_USM_v1.5.xlsx
@@ -264,16 +264,16 @@
     <t>Peripheral</t>
   </si>
   <si>
-    <t>0.3mm 10P 0.5mm 60mm P=0.5mm FFC Cable (Flexible Flat Cable) ROHS</t>
-  </si>
-  <si>
     <t>P=0.5mm</t>
   </si>
   <si>
-    <t>AB03A0100000180A</t>
-  </si>
-  <si>
-    <t>BZCN</t>
+    <t>JS05B-10P-100-3-4</t>
+  </si>
+  <si>
+    <t>JUSHUO</t>
+  </si>
+  <si>
+    <t>0.3mm 10P 0.5mm Reverse 10cm P=0.5mm FFC Cable (Flexible Flat Cable) ROHS</t>
   </si>
 </sst>
 </file>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="K15" s="7"/>
     </row>
-    <row r="16" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="11">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1255,16 +1255,16 @@
         <v>79</v>
       </c>
       <c r="E16" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="F16" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="G16" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="H16" s="9" t="s">
         <v>83</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>84</v>
       </c>
       <c r="I16" s="10" t="s">
         <v>79</v>
